--- a/grafici-Alessandro-Pigazzini-20595A..xlsx
+++ b/grafici-Alessandro-Pigazzini-20595A..xlsx
@@ -8,31 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pigal.LAPTOP-J221DV7B\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422B203F-03F3-4231-A3C5-776AFA84D215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C71C227-A0E5-4B2E-9715-7B47C11B9EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{6370E8D3-F648-4909-BD0F-C6F9D7005C9D}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Foglio1!$B$139:$B$142</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Foglio1!$C$138</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Foglio1!$F$97</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Foglio1!$F$98:$F$103</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Foglio1!$C$139:$C$142</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Foglio1!$B$98:$B$103</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Foglio1!$C$97</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Foglio1!$C$98:$C$103</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Foglio1!$D$97</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Foglio1!$D$98:$D$103</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Foglio1!$E$97</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Foglio1!$E$98:$E$103</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -57,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="93">
   <si>
     <t>percentuali %</t>
   </si>
@@ -280,6 +262,63 @@
   <si>
     <t>Espressione        personale</t>
   </si>
+  <si>
+    <t>graffiti</t>
+  </si>
+  <si>
+    <t>colori</t>
+  </si>
+  <si>
+    <t>stili</t>
+  </si>
+  <si>
+    <t>superfici</t>
+  </si>
+  <si>
+    <t>totale</t>
+  </si>
+  <si>
+    <t>argento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">graffiti </t>
+  </si>
+  <si>
+    <t>tag/sticker</t>
+  </si>
+  <si>
+    <t>throw up</t>
+  </si>
+  <si>
+    <t>bubble</t>
+  </si>
+  <si>
+    <t>wild</t>
+  </si>
+  <si>
+    <t>block buster</t>
+  </si>
+  <si>
+    <t>3d</t>
+  </si>
+  <si>
+    <t>stencil</t>
+  </si>
+  <si>
+    <t>12 in comune</t>
+  </si>
+  <si>
+    <t>treni</t>
+  </si>
+  <si>
+    <t>tunnel</t>
+  </si>
+  <si>
+    <t>autostrade</t>
+  </si>
+  <si>
+    <t>monumenti</t>
+  </si>
 </sst>
 </file>
 
@@ -322,7 +361,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -330,11 +369,91 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -353,6 +472,18 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -12034,282 +12165,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Foglio1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>città</v>
-          </cell>
-          <cell r="B1" t="str">
-            <v>percentuale</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Foglio1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="5">
-          <cell r="C5" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D5">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="C6" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D6">
-            <v>72</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="C7" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D7">
-            <v>60</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="C8" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D8">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="C9" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D9">
-            <v>56</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="C10" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D10">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="C11" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D11">
-            <v>53</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="C12" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D12">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="C13" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D13">
-            <v>18</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="C14" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D14">
-            <v>31</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="C15" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D15">
-            <v>62</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="C16" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D16">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="C17" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D17">
-            <v>28</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="C18" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D18">
-            <v>70</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="C19" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D19">
-            <v>29</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="C20" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D20">
-            <v>60</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="C21" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D21">
-            <v>48</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="C22" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D22">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="C23" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D23">
-            <v>49</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="C24" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D24">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="C25" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D25">
-            <v>55</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="C26" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D26">
-            <v>48</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="C27" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D27">
-            <v>55</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="C28" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D28">
-            <v>76</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="C29" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D29">
-            <v>18</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="C30" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D30">
-            <v>39</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="C31" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D31">
-            <v>50</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="C32" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D32">
-            <v>56</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="C33" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D33">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="C34" t="e">
-            <v>#VALUE!</v>
-          </cell>
-          <cell r="D34">
-            <v>49</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
@@ -12627,7 +12482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A627C68C-BF48-494F-A4CE-DB5A79B37709}">
-  <dimension ref="B4:Q208"/>
+  <dimension ref="B4:AC208"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="22.36328125" customWidth="1"/>
@@ -12759,7 +12614,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>63</v>
       </c>
@@ -12767,7 +12622,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>19</v>
       </c>
@@ -12775,7 +12630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>18</v>
       </c>
@@ -12783,7 +12638,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>58</v>
       </c>
@@ -12791,7 +12646,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>17</v>
       </c>
@@ -12799,23 +12654,375 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="7">
         <v>19</v>
       </c>
+      <c r="R28" s="11"/>
+      <c r="S28" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="T28" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="U28" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="V28" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="W28" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="X28" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y28" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z28" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="12"/>
+      <c r="AB28" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC28" s="13" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="7">
         <v>49.5</v>
       </c>
+      <c r="R29" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="S29" s="15">
+        <v>24</v>
+      </c>
+      <c r="T29" s="15">
+        <v>36</v>
+      </c>
+      <c r="U29" s="15">
+        <v>48</v>
+      </c>
+      <c r="V29" s="15">
+        <v>66</v>
+      </c>
+      <c r="W29" s="15">
+        <v>72</v>
+      </c>
+      <c r="X29" s="15">
+        <v>90</v>
+      </c>
+      <c r="Y29" s="15">
+        <v>120</v>
+      </c>
+      <c r="Z29" s="15">
+        <v>144</v>
+      </c>
+      <c r="AA29" s="15"/>
+      <c r="AB29" s="15">
+        <f>SUM(S29:AA29)</f>
+        <v>600</v>
+      </c>
+      <c r="AC29" s="16">
+        <v>200</v>
+      </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="R30" s="14"/>
+      <c r="S30" s="15"/>
+      <c r="T30" s="15"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="15"/>
+      <c r="W30" s="15"/>
+      <c r="X30" s="15"/>
+      <c r="Y30" s="15"/>
+      <c r="Z30" s="15"/>
+      <c r="AA30" s="15"/>
+      <c r="AB30" s="15"/>
+      <c r="AC30" s="16"/>
+    </row>
+    <row r="31" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="R31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="S31" s="18">
+        <f>S29*100/$AB$29</f>
+        <v>4</v>
+      </c>
+      <c r="T31" s="18">
+        <f t="shared" ref="T31:Z31" si="0">T29*100/$AB$29</f>
+        <v>6</v>
+      </c>
+      <c r="U31" s="18">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="V31" s="18">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="W31" s="18">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="X31" s="18">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="Y31" s="18">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Z31" s="18">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="AA31" s="18"/>
+      <c r="AB31" s="18"/>
+      <c r="AC31" s="19"/>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="R35" s="11"/>
+      <c r="S35" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="T35" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="U35" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="V35" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="W35" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="X35" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y35" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z35" s="12"/>
+      <c r="AA35" s="12"/>
+      <c r="AB35" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC35" s="13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="R36" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="S36" s="15">
+        <v>4</v>
+      </c>
+      <c r="T36" s="15">
+        <v>8</v>
+      </c>
+      <c r="U36" s="15">
+        <v>14</v>
+      </c>
+      <c r="V36" s="15">
+        <v>24</v>
+      </c>
+      <c r="W36" s="15">
+        <v>30</v>
+      </c>
+      <c r="X36" s="15">
+        <v>56</v>
+      </c>
+      <c r="Y36" s="15">
+        <v>76</v>
+      </c>
+      <c r="Z36" s="15"/>
+      <c r="AA36" s="15"/>
+      <c r="AB36" s="15">
+        <f>SUM(S36:AA36)</f>
+        <v>212</v>
+      </c>
+      <c r="AC36" s="16">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="R37" s="14"/>
+      <c r="S37" s="15"/>
+      <c r="T37" s="15"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="15"/>
+      <c r="W37" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="X37" s="10"/>
+      <c r="Y37" s="15"/>
+      <c r="Z37" s="15"/>
+      <c r="AA37" s="15"/>
+      <c r="AB37" s="15"/>
+      <c r="AC37" s="16"/>
+    </row>
+    <row r="38" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="R38" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="S38" s="18">
+        <f>S36*100/$AC$36</f>
+        <v>2</v>
+      </c>
+      <c r="T38" s="18">
+        <f t="shared" ref="T38:Y38" si="1">T36*100/$AC$36</f>
+        <v>4</v>
+      </c>
+      <c r="U38" s="18">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="V38" s="18">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="W38" s="18">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="X38" s="18">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="Y38" s="18">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="Z38" s="18"/>
+      <c r="AA38" s="18"/>
+      <c r="AB38" s="18"/>
+      <c r="AC38" s="19"/>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="R42" s="11"/>
+      <c r="S42" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="T42" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="U42" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="V42" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="W42" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="X42" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y42" s="12"/>
+      <c r="Z42" s="12"/>
+      <c r="AA42" s="12"/>
+      <c r="AB42" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC42" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="R43" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="S43" s="15">
+        <v>6</v>
+      </c>
+      <c r="T43" s="15">
+        <v>11</v>
+      </c>
+      <c r="U43" s="15">
+        <v>20</v>
+      </c>
+      <c r="V43" s="15">
+        <v>26</v>
+      </c>
+      <c r="W43" s="15">
+        <v>38</v>
+      </c>
+      <c r="X43" s="15">
+        <v>99</v>
+      </c>
+      <c r="Y43" s="15"/>
+      <c r="Z43" s="15"/>
+      <c r="AA43" s="15"/>
+      <c r="AB43" s="15">
+        <f>SUM(S43:X43)</f>
+        <v>200</v>
+      </c>
+      <c r="AC43" s="16">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="R44" s="14"/>
+      <c r="S44" s="15"/>
+      <c r="T44" s="15"/>
+      <c r="U44" s="15"/>
+      <c r="V44" s="15"/>
+      <c r="W44" s="15"/>
+      <c r="X44" s="15"/>
+      <c r="Y44" s="15"/>
+      <c r="Z44" s="15"/>
+      <c r="AA44" s="15"/>
+      <c r="AB44" s="15"/>
+      <c r="AC44" s="16"/>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.35">
+      <c r="R45" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="S45" s="18">
+        <f>S43*100/$AC$43</f>
+        <v>3</v>
+      </c>
+      <c r="T45" s="18">
+        <f>T43*100/$AC$43</f>
+        <v>5.5</v>
+      </c>
+      <c r="U45" s="18">
+        <f>U43*100/$AC$43</f>
+        <v>10</v>
+      </c>
+      <c r="V45" s="18">
+        <f>V43*100/$AC$43</f>
+        <v>13</v>
+      </c>
+      <c r="W45" s="18">
+        <f>W43*100/$AC$43</f>
+        <v>19</v>
+      </c>
+      <c r="X45" s="18">
+        <f>X43*100/$AC$43</f>
+        <v>49.5</v>
+      </c>
+      <c r="Y45" s="18"/>
+      <c r="Z45" s="18"/>
+      <c r="AA45" s="18"/>
+      <c r="AB45" s="18"/>
+      <c r="AC45" s="19"/>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>64</v>
       </c>
@@ -12826,7 +13033,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>23</v>
       </c>
@@ -12837,7 +13044,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>27</v>
       </c>
@@ -13353,6 +13560,9 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B206:C208">
     <sortCondition ref="C206:C208"/>
   </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="W37:X37"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <drawing r:id="rId2"/>
